--- a/data/trans_dic/P22$ss-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P22$ss-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguridad Social</t>
+          <t>Población que, al menos, es beneficiaria de la Seguridad Social (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,59; 94,62</t>
+          <t>87,67; 94,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,06; 96,8</t>
+          <t>91,27; 96,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95,31; 99,05</t>
+          <t>95,38; 99,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94,29; 98,41</t>
+          <t>94,37; 98,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,33; 98,31</t>
+          <t>93,2; 98,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,44; 98,58</t>
+          <t>94,0; 98,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,55; 98,85</t>
+          <t>94,85; 98,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>95,13; 98,03</t>
+          <t>95,18; 97,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,55; 95,82</t>
+          <t>91,7; 96,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93,65; 97,35</t>
+          <t>93,41; 97,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95,73; 98,6</t>
+          <t>95,82; 98,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,31; 97,82</t>
+          <t>95,38; 97,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,8; 97,41</t>
+          <t>93,58; 97,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,93; 96,09</t>
+          <t>91,17; 96,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,63; 99,16</t>
+          <t>96,66; 99,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94,09; 98,19</t>
+          <t>94,12; 98,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,59; 97,23</t>
+          <t>93,69; 97,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,6; 96,32</t>
+          <t>91,65; 96,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,87; 98,04</t>
+          <t>94,91; 98,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>95,99; 98,25</t>
+          <t>96,06; 98,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>94,26; 96,89</t>
+          <t>94,18; 96,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92,15; 95,63</t>
+          <t>92,28; 95,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96,35; 98,24</t>
+          <t>96,28; 98,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,56; 97,93</t>
+          <t>95,71; 98,0</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94,24; 98,27</t>
+          <t>94,22; 98,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,46; 97,08</t>
+          <t>91,76; 97,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,06; 95,07</t>
+          <t>89,26; 94,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94,81; 98,76</t>
+          <t>94,22; 98,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>95,8; 98,91</t>
+          <t>95,68; 98,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>94,61; 98,78</t>
+          <t>94,5; 98,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,0; 98,07</t>
+          <t>94,03; 98,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>97,37; 99,35</t>
+          <t>97,25; 99,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95,75; 98,44</t>
+          <t>95,83; 98,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94,1; 97,45</t>
+          <t>94,25; 97,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92,65; 95,99</t>
+          <t>92,58; 96,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>96,43; 98,8</t>
+          <t>96,58; 98,8</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,5; 95,94</t>
+          <t>90,37; 95,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,61; 95,77</t>
+          <t>89,6; 95,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,5; 97,33</t>
+          <t>92,34; 97,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90,17; 96,12</t>
+          <t>90,06; 95,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,61; 97,93</t>
+          <t>93,87; 97,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,66; 97,01</t>
+          <t>92,45; 96,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,22; 98,96</t>
+          <t>95,33; 98,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>95,28; 98,44</t>
+          <t>95,02; 98,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,77; 96,36</t>
+          <t>93,03; 96,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,14; 95,81</t>
+          <t>91,95; 95,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94,68; 97,75</t>
+          <t>94,67; 97,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,78; 97,05</t>
+          <t>93,84; 97,2</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,98; 97,16</t>
+          <t>90,77; 97,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95,07; 99,5</t>
+          <t>94,8; 99,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,59; 97,56</t>
+          <t>90,52; 97,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94,13; 98,28</t>
+          <t>93,61; 98,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,21; 94,69</t>
+          <t>86,8; 94,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,63; 99,08</t>
+          <t>94,49; 99,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,98; 99,6</t>
+          <t>96,17; 99,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>95,72; 98,57</t>
+          <t>95,83; 98,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90,11; 95,32</t>
+          <t>90,01; 95,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95,54; 98,6</t>
+          <t>95,68; 98,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94,28; 98,2</t>
+          <t>94,43; 98,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,65; 98,17</t>
+          <t>95,63; 98,14</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90,88; 96,53</t>
+          <t>91,03; 96,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,57; 97,67</t>
+          <t>91,89; 97,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91,3; 97,45</t>
+          <t>91,55; 97,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96,35; 98,96</t>
+          <t>96,3; 98,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>93,93; 98,25</t>
+          <t>93,84; 98,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94,34; 98,91</t>
+          <t>94,17; 98,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96,75; 99,65</t>
+          <t>96,47; 99,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>96,01; 98,66</t>
+          <t>96,12; 98,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,42; 96,91</t>
+          <t>93,45; 96,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>93,98; 97,83</t>
+          <t>94,14; 97,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94,8; 98,16</t>
+          <t>94,67; 98,11</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>96,73; 98,58</t>
+          <t>96,64; 98,56</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95,24; 98,11</t>
+          <t>95,31; 98,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94,01; 97,46</t>
+          <t>94,05; 97,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90,66; 95,06</t>
+          <t>90,71; 95,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93,25; 97,54</t>
+          <t>93,04; 97,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,32; 97,42</t>
+          <t>94,08; 97,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,25; 98,18</t>
+          <t>95,32; 98,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,49; 96,68</t>
+          <t>93,39; 96,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>95,22; 98,76</t>
+          <t>95,31; 98,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95,42; 97,52</t>
+          <t>95,22; 97,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95,32; 97,51</t>
+          <t>95,24; 97,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92,8; 95,35</t>
+          <t>92,73; 95,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,14; 97,92</t>
+          <t>95,16; 98,01</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>96,16; 98,47</t>
+          <t>96,09; 98,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94,28; 97,54</t>
+          <t>94,48; 97,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93,25; 96,47</t>
+          <t>93,24; 96,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95,68; 98,88</t>
+          <t>95,7; 98,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>91,85; 95,48</t>
+          <t>91,96; 95,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>94,86; 97,85</t>
+          <t>94,68; 97,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,58; 96,75</t>
+          <t>93,45; 96,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>94,62; 97,11</t>
+          <t>94,53; 97,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>94,47; 96,57</t>
+          <t>94,33; 96,48</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95,12; 97,37</t>
+          <t>95,12; 97,33</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94,01; 96,21</t>
+          <t>94,12; 96,2</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>95,62; 97,99</t>
+          <t>95,7; 98,12</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>94,93; 96,41</t>
+          <t>95,02; 96,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>94,31; 95,94</t>
+          <t>94,45; 96,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94,27; 95,92</t>
+          <t>94,34; 95,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95,78; 97,37</t>
+          <t>95,77; 97,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>94,72; 96,16</t>
+          <t>94,67; 96,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>95,61; 97,01</t>
+          <t>95,6; 97,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>95,87; 97,12</t>
+          <t>95,75; 97,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>96,47; 97,7</t>
+          <t>96,53; 97,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>95,06; 96,09</t>
+          <t>95,01; 96,03</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95,3; 96,31</t>
+          <t>95,28; 96,34</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>95,25; 96,29</t>
+          <t>95,35; 96,29</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>96,34; 97,32</t>
+          <t>96,37; 97,39</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguridad Social</t>
+          <t>Población que, al menos, es beneficiaria de la Seguridad Social (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>238304; 257445</t>
+          <t>238530; 257642</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>268398; 285317</t>
+          <t>269012; 285688</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>279997; 290972</t>
+          <t>280199; 291707</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>293673; 306506</t>
+          <t>293907; 306233</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>243443; 256443</t>
+          <t>243103; 256408</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>271262; 283177</t>
+          <t>270023; 282940</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>272051; 284427</t>
+          <t>272909; 284755</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>275530; 283940</t>
+          <t>275669; 283820</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>487889; 510620</t>
+          <t>488712; 511873</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>545034; 566535</t>
+          <t>543611; 565393</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>556665; 573353</t>
+          <t>557197; 573565</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>572875; 587971</t>
+          <t>573324; 588100</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>462521; 480310</t>
+          <t>461418; 480205</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>458779; 484812</t>
+          <t>459997; 484547</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>485632; 498348</t>
+          <t>485764; 498363</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>487760; 508989</t>
+          <t>487898; 509436</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>471627; 490006</t>
+          <t>472173; 490596</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>479775; 504507</t>
+          <t>480027; 504763</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>496274; 512814</t>
+          <t>496438; 513519</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>494297; 505961</t>
+          <t>494695; 506460</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>939777; 966011</t>
+          <t>938983; 966925</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>947613; 983386</t>
+          <t>948881; 983383</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>988225; 1007565</t>
+          <t>987555; 1007631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>987501; 1011933</t>
+          <t>989052; 1012706</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>300465; 313319</t>
+          <t>300413; 313708</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>296375; 314589</t>
+          <t>297338; 314464</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>282016; 301054</t>
+          <t>282666; 300795</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>299648; 312122</t>
+          <t>297795; 312112</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>321331; 331756</t>
+          <t>320927; 331723</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>322641; 336856</t>
+          <t>322259; 337072</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>316143; 329824</t>
+          <t>316241; 329790</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>339954; 346846</t>
+          <t>339539; 346850</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>626471; 644066</t>
+          <t>626986; 643770</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>625810; 648122</t>
+          <t>626804; 648635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>604974; 626772</t>
+          <t>604550; 626853</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>641451; 657199</t>
+          <t>642404; 657201</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>322659; 342053</t>
+          <t>322188; 341563</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>335132; 358146</t>
+          <t>335084; 358003</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>342200; 360090</t>
+          <t>341628; 359231</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>281848; 300428</t>
+          <t>281488; 299859</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>346928; 362955</t>
+          <t>347882; 362739</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>360386; 377325</t>
+          <t>359580; 376929</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>368754; 383249</t>
+          <t>369205; 383256</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>453242; 468303</t>
+          <t>452021; 467976</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>674576; 700649</t>
+          <t>676426; 701016</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>702988; 730953</t>
+          <t>701527; 729380</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>716961; 740184</t>
+          <t>716913; 739627</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>739250; 765023</t>
+          <t>739701; 766233</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>182942; 197534</t>
+          <t>184549; 197871</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202137; 211546</t>
+          <t>201559; 210654</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>191354; 206065</t>
+          <t>191200; 205705</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168251; 175664</t>
+          <t>167313; 175567</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>179023; 196650</t>
+          <t>180252; 196855</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>207810; 217569</t>
+          <t>207495; 217499</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>209791; 217705</t>
+          <t>210219; 217708</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>199731; 205682</t>
+          <t>199946; 205695</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>370311; 391729</t>
+          <t>369939; 391314</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>412950; 426172</t>
+          <t>413542; 426300</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>405213; 422072</t>
+          <t>405848; 421981</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>370540; 380325</t>
+          <t>370475; 380208</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>246118; 261402</t>
+          <t>246530; 261797</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>250882; 267585</t>
+          <t>251748; 267618</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240222; 256403</t>
+          <t>240884; 256379</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>259791; 266840</t>
+          <t>259670; 266463</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>261273; 273281</t>
+          <t>261019; 273522</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>264191; 276992</t>
+          <t>263693; 276791</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>264242; 272170</t>
+          <t>263468; 272174</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>246798; 253601</t>
+          <t>247081; 253916</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>512835; 532001</t>
+          <t>512983; 531745</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>520658; 541964</t>
+          <t>521573; 542205</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>508338; 526364</t>
+          <t>507656; 526105</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>509485; 519192</t>
+          <t>509015; 519084</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>584800; 602399</t>
+          <t>585206; 602697</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623056; 645934</t>
+          <t>623361; 646587</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>592534; 621264</t>
+          <t>592842; 622329</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>582111; 608918</t>
+          <t>580798; 608563</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>600861; 620600</t>
+          <t>599321; 620779</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>660927; 681218</t>
+          <t>661374; 681982</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>641747; 663668</t>
+          <t>641103; 663236</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>808478; 838566</t>
+          <t>809251; 837921</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1193758; 1219992</t>
+          <t>1191288; 1219334</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1293117; 1322926</t>
+          <t>1292130; 1321852</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1243545; 1277663</t>
+          <t>1242551; 1278863</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1401804; 1442780</t>
+          <t>1402003; 1444118</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>713034; 730124</t>
+          <t>712503; 730209</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>734554; 759906</t>
+          <t>736122; 759400</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>726058; 751063</t>
+          <t>725950; 750917</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>888590; 918327</t>
+          <t>888794; 918596</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>719658; 748057</t>
+          <t>720499; 747058</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>781483; 806151</t>
+          <t>780026; 805574</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>773149; 799345</t>
+          <t>772018; 799300</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>676912; 694695</t>
+          <t>676264; 694448</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1440589; 1472662</t>
+          <t>1438537; 1471239</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1524682; 1560722</t>
+          <t>1524658; 1560110</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1508665; 1543955</t>
+          <t>1510378; 1543727</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1572105; 1611042</t>
+          <t>1573383; 1613243</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3104184; 3152618</t>
+          <t>3107381; 3153465</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3230977; 3286587</t>
+          <t>3235833; 3289280</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3195178; 3251103</t>
+          <t>3197578; 3248907</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3313703; 3368767</t>
+          <t>3313369; 3370348</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3198770; 3247499</t>
+          <t>3197097; 3246151</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3401956; 3451750</t>
+          <t>3401818; 3453496</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3392445; 3436861</t>
+          <t>3388285; 3433545</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3530609; 3575358</t>
+          <t>3532799; 3573450</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6319080; 6387327</t>
+          <t>6315493; 6383131</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6656193; 6726464</t>
+          <t>6654781; 6728209</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6599057; 6671207</t>
+          <t>6606123; 6671010</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6859215; 6928461</t>
+          <t>6861345; 6933410</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$ss-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P22$ss-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,67; 94,69</t>
+          <t>88,15; 95,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,27; 96,93</t>
+          <t>91,51; 96,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95,38; 99,3</t>
+          <t>95,33; 99,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94,37; 98,33</t>
+          <t>94,94; 98,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,2; 98,3</t>
+          <t>93,58; 98,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,0; 98,5</t>
+          <t>94,39; 98,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,85; 98,97</t>
+          <t>94,67; 98,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>95,18; 97,99</t>
+          <t>95,7; 98,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,7; 96,05</t>
+          <t>91,44; 95,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93,41; 97,15</t>
+          <t>93,54; 97,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95,82; 98,64</t>
+          <t>95,87; 98,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,38; 97,84</t>
+          <t>95,9; 98,12</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,58; 97,39</t>
+          <t>93,83; 97,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,17; 96,04</t>
+          <t>90,7; 96,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,66; 99,16</t>
+          <t>96,66; 99,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94,12; 98,27</t>
+          <t>94,42; 98,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,69; 97,35</t>
+          <t>93,66; 97,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,65; 96,37</t>
+          <t>91,49; 96,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,91; 98,17</t>
+          <t>94,71; 98,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>96,06; 98,35</t>
+          <t>95,91; 98,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>94,18; 96,98</t>
+          <t>94,4; 97,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92,28; 95,63</t>
+          <t>92,1; 95,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96,28; 98,24</t>
+          <t>96,25; 98,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,71; 98,0</t>
+          <t>95,83; 98,12</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94,22; 98,39</t>
+          <t>94,05; 98,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,76; 97,04</t>
+          <t>91,61; 97,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,26; 94,99</t>
+          <t>89,1; 95,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94,22; 98,75</t>
+          <t>93,84; 98,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>95,68; 98,9</t>
+          <t>95,77; 98,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>94,5; 98,84</t>
+          <t>94,14; 98,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,03; 98,06</t>
+          <t>94,34; 98,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>97,25; 99,35</t>
+          <t>97,46; 99,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95,83; 98,4</t>
+          <t>95,67; 98,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94,25; 97,53</t>
+          <t>94,33; 97,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92,58; 96,0</t>
+          <t>92,6; 96,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>96,58; 98,8</t>
+          <t>96,45; 98,69</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,37; 95,81</t>
+          <t>90,77; 96,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,6; 95,73</t>
+          <t>89,95; 95,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,34; 97,1</t>
+          <t>92,37; 97,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90,06; 95,94</t>
+          <t>90,95; 96,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,87; 97,88</t>
+          <t>93,89; 97,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,45; 96,91</t>
+          <t>92,48; 96,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,33; 98,96</t>
+          <t>95,31; 99,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>95,02; 98,37</t>
+          <t>94,29; 97,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93,03; 96,41</t>
+          <t>93,18; 96,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91,95; 95,6</t>
+          <t>91,99; 95,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94,67; 97,67</t>
+          <t>94,84; 97,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,84; 97,2</t>
+          <t>93,32; 96,55</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>90,77; 97,33</t>
+          <t>90,55; 97,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,8; 99,08</t>
+          <t>94,92; 99,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,52; 97,39</t>
+          <t>90,63; 97,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93,61; 98,22</t>
+          <t>94,02; 98,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,8; 94,79</t>
+          <t>86,69; 94,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,49; 99,05</t>
+          <t>94,49; 98,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,17; 99,6</t>
+          <t>96,01; 99,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>95,83; 98,58</t>
+          <t>96,2; 98,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90,01; 95,22</t>
+          <t>89,85; 95,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95,68; 98,63</t>
+          <t>95,56; 98,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94,43; 98,18</t>
+          <t>94,02; 98,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,63; 98,14</t>
+          <t>95,78; 98,16</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>91,03; 96,67</t>
+          <t>90,85; 96,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,89; 97,68</t>
+          <t>91,24; 97,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91,55; 97,44</t>
+          <t>91,41; 97,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96,3; 98,82</t>
+          <t>96,09; 98,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>93,84; 98,34</t>
+          <t>94,02; 98,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94,17; 98,84</t>
+          <t>94,37; 98,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96,47; 99,66</t>
+          <t>96,42; 99,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>96,12; 98,78</t>
+          <t>96,08; 98,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,45; 96,86</t>
+          <t>93,39; 97,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>94,14; 97,87</t>
+          <t>94,16; 97,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94,67; 98,11</t>
+          <t>94,72; 98,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>96,64; 98,56</t>
+          <t>96,76; 98,54</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95,31; 98,16</t>
+          <t>95,19; 98,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94,05; 97,56</t>
+          <t>93,91; 97,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90,71; 95,22</t>
+          <t>90,84; 95,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93,04; 97,48</t>
+          <t>93,0; 96,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,08; 97,45</t>
+          <t>94,46; 97,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,32; 98,29</t>
+          <t>95,12; 98,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,39; 96,62</t>
+          <t>93,3; 96,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>95,31; 98,68</t>
+          <t>94,64; 97,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95,22; 97,46</t>
+          <t>95,29; 97,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95,24; 97,44</t>
+          <t>95,28; 97,43</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92,73; 95,44</t>
+          <t>92,74; 95,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,16; 98,01</t>
+          <t>94,41; 97,02</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>96,09; 98,48</t>
+          <t>96,19; 98,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94,48; 97,47</t>
+          <t>94,17; 97,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93,24; 96,45</t>
+          <t>93,23; 96,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95,7; 98,91</t>
+          <t>94,5; 97,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>91,96; 95,35</t>
+          <t>91,79; 95,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>94,68; 97,78</t>
+          <t>94,75; 97,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,45; 96,75</t>
+          <t>93,69; 96,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>94,53; 97,07</t>
+          <t>94,91; 97,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>94,33; 96,48</t>
+          <t>94,51; 96,63</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95,12; 97,33</t>
+          <t>95,08; 97,34</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94,12; 96,2</t>
+          <t>93,84; 96,27</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>95,7; 98,12</t>
+          <t>95,1; 96,94</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>95,02; 96,43</t>
+          <t>95,01; 96,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>94,45; 96,02</t>
+          <t>94,45; 96,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94,34; 95,85</t>
+          <t>94,42; 95,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95,77; 97,41</t>
+          <t>95,38; 96,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>94,67; 96,12</t>
+          <t>94,7; 96,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>95,6; 97,05</t>
+          <t>95,58; 96,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>95,75; 97,03</t>
+          <t>95,83; 97,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>96,53; 97,64</t>
+          <t>96,42; 97,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>95,01; 96,03</t>
+          <t>95,04; 96,13</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95,28; 96,34</t>
+          <t>95,28; 96,32</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>95,35; 96,29</t>
+          <t>95,37; 96,31</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>96,37; 97,39</t>
+          <t>96,11; 96,97</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>301420</t>
+          <t>309462</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>280569</t>
+          <t>307273</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>581988</t>
+          <t>616735</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>238530; 257642</t>
+          <t>239844; 258691</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>269012; 285688</t>
+          <t>269716; 285297</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>280199; 291707</t>
+          <t>280031; 291127</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>293907; 306233</t>
+          <t>302704; 314015</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>243103; 256408</t>
+          <t>244081; 256610</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>270023; 282940</t>
+          <t>271121; 283108</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>272909; 284755</t>
+          <t>272397; 284272</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>275669; 283820</t>
+          <t>302470; 310683</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>488712; 511873</t>
+          <t>487316; 510550</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>543611; 565393</t>
+          <t>544404; 565285</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>557197; 573565</t>
+          <t>557476; 573329</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>573324; 588100</t>
+          <t>608886; 622963</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501239</t>
+          <t>513216</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>501175</t>
+          <t>532570</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1002414</t>
+          <t>1045787</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>461418; 480205</t>
+          <t>462661; 480406</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>459997; 484547</t>
+          <t>457648; 484445</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>485764; 498363</t>
+          <t>485808; 498396</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>487898; 509436</t>
+          <t>501031; 521386</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>472173; 490596</t>
+          <t>471985; 490011</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>480027; 504763</t>
+          <t>479179; 505234</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>496438; 513519</t>
+          <t>495395; 512665</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>494695; 506460</t>
+          <t>524140; 537644</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>938983; 966925</t>
+          <t>941162; 967137</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>948881; 983383</t>
+          <t>947106; 982171</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>987555; 1007631</t>
+          <t>987191; 1008177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>989052; 1012706</t>
+          <t>1032237; 1056858</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307221</t>
+          <t>306185</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>344300</t>
+          <t>351548</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>651521</t>
+          <t>657734</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>300413; 313708</t>
+          <t>299877; 313372</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>297338; 314464</t>
+          <t>296865; 314472</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>282666; 300795</t>
+          <t>282165; 300899</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>297795; 312112</t>
+          <t>296519; 311294</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>320927; 331723</t>
+          <t>321240; 331800</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>322259; 337072</t>
+          <t>321036; 336892</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>316241; 329790</t>
+          <t>317269; 329886</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>339539; 346850</t>
+          <t>347311; 354033</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>626986; 643770</t>
+          <t>625943; 643030</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>626804; 648635</t>
+          <t>627359; 648806</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>604550; 626853</t>
+          <t>604632; 627710</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>642404; 657201</t>
+          <t>648513; 663590</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>292366</t>
+          <t>351059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>461084</t>
+          <t>405712</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>753450</t>
+          <t>756772</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>322188; 341563</t>
+          <t>323620; 342335</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>335084; 358003</t>
+          <t>336402; 357183</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>341628; 359231</t>
+          <t>341736; 359722</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>281488; 299859</t>
+          <t>339361; 359015</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>347882; 362739</t>
+          <t>347975; 362745</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>359580; 376929</t>
+          <t>359690; 377104</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>369205; 383256</t>
+          <t>369104; 383858</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>452021; 467976</t>
+          <t>397848; 411286</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>676426; 701016</t>
+          <t>677505; 701545</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>701527; 729380</t>
+          <t>701802; 730508</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>716913; 739627</t>
+          <t>718186; 739774</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>739701; 766233</t>
+          <t>742010; 767680</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172581</t>
+          <t>199074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>203586</t>
+          <t>221871</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>376167</t>
+          <t>420943</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>184549; 197871</t>
+          <t>184096; 198246</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>201559; 210654</t>
+          <t>201819; 210659</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>191200; 205705</t>
+          <t>191438; 206212</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>167313; 175567</t>
+          <t>193376; 202435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>180252; 196855</t>
+          <t>180035; 196504</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>207495; 217499</t>
+          <t>207482; 217227</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>210219; 217708</t>
+          <t>209865; 217714</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>199946; 205695</t>
+          <t>218591; 224518</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>369939; 391314</t>
+          <t>369272; 390814</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>413542; 426300</t>
+          <t>413025; 426355</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>405848; 421981</t>
+          <t>404092; 422070</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>370475; 380208</t>
+          <t>414623; 424920</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263856</t>
+          <t>264997</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>251051</t>
+          <t>257583</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>514907</t>
+          <t>522579</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>246530; 261797</t>
+          <t>246034; 260910</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>251748; 267618</t>
+          <t>249971; 267553</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240884; 256379</t>
+          <t>240532; 256507</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>259670; 266463</t>
+          <t>260116; 267673</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>261019; 273522</t>
+          <t>261525; 273204</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>263693; 276791</t>
+          <t>264263; 276294</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>263468; 272174</t>
+          <t>263331; 272096</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>247081; 253916</t>
+          <t>253420; 260779</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>512983; 531745</t>
+          <t>512654; 532628</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>521573; 542205</t>
+          <t>521647; 542176</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>507656; 526105</t>
+          <t>507945; 526598</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>509015; 519084</t>
+          <t>517165; 526680</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>599383</t>
+          <t>686649</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>824415</t>
+          <t>743913</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1423799</t>
+          <t>1430562</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>585206; 602697</t>
+          <t>584477; 602636</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623361; 646587</t>
+          <t>622450; 646243</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>592842; 622329</t>
+          <t>593706; 621380</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>580798; 608563</t>
+          <t>669313; 697780</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>599321; 620779</t>
+          <t>601743; 620790</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>661374; 681982</t>
+          <t>659983; 680845</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>641103; 663236</t>
+          <t>640474; 663096</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>809251; 837921</t>
+          <t>729632; 753091</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1191288; 1219334</t>
+          <t>1192118; 1219608</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1292130; 1321852</t>
+          <t>1292622; 1321710</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1242551; 1278863</t>
+          <t>1242718; 1278598</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1402003; 1444118</t>
+          <t>1407330; 1446266</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>902799</t>
+          <t>767550</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>687006</t>
+          <t>798746</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1589806</t>
+          <t>1566296</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>712503; 730209</t>
+          <t>713234; 729982</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>736122; 759400</t>
+          <t>733707; 759776</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>725950; 750917</t>
+          <t>725911; 751346</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>888794; 918596</t>
+          <t>754212; 777998</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>720499; 747058</t>
+          <t>719170; 748024</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>780026; 805574</t>
+          <t>780610; 806416</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>772018; 799300</t>
+          <t>774069; 800199</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>676264; 694448</t>
+          <t>788356; 808198</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1438537; 1471239</t>
+          <t>1441268; 1473541</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1524658; 1560110</t>
+          <t>1524068; 1560271</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1510378; 1543727</t>
+          <t>1505949; 1544913</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1573383; 1613243</t>
+          <t>1548813; 1578862</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3340866</t>
+          <t>3398193</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3553187</t>
+          <t>3619216</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6894053</t>
+          <t>7017410</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3107381; 3153465</t>
+          <t>3106908; 3151417</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3235833; 3289280</t>
+          <t>3235543; 3289252</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3197578; 3248907</t>
+          <t>3200247; 3250951</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3313369; 3370348</t>
+          <t>3369388; 3420935</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3197097; 3246151</t>
+          <t>3198295; 3247317</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3401818; 3453496</t>
+          <t>3401162; 3450549</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3388285; 3433545</t>
+          <t>3391242; 3434231</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3532799; 3573450</t>
+          <t>3599760; 3635232</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6315493; 6383131</t>
+          <t>6317930; 6390272</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6654781; 6728209</t>
+          <t>6654579; 6727068</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6606123; 6671010</t>
+          <t>6607416; 6672500</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6861345; 6933410</t>
+          <t>6983679; 7046356</t>
         </is>
       </c>
     </row>
